--- a/database/excels/myhistory/base-seeder.xlsx
+++ b/database/excels/myhistory/base-seeder.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/monoland/Platform/monoland/database/excels/myhistory/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AD1B096-9D23-2F4C-8CCD-BB9E71D5D625}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7AB6C9D-141A-1E46-A66E-6CF39B444C4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" xr2:uid="{94E1010F-4E68-D749-BBCF-3803F804C4FE}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" activeTab="5" xr2:uid="{94E1010F-4E68-D749-BBCF-3803F804C4FE}"/>
   </bookViews>
   <sheets>
     <sheet name="module" sheetId="2" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="77">
   <si>
     <t>name</t>
   </si>
@@ -249,6 +249,18 @@
   </si>
   <si>
     <t>green</t>
+  </si>
+  <si>
+    <t>Riwayat Pindah Instansi</t>
+  </si>
+  <si>
+    <t>myhistory-instancy</t>
+  </si>
+  <si>
+    <t>instancy</t>
+  </si>
+  <si>
+    <t>home_work</t>
   </si>
 </sst>
 </file>
@@ -685,7 +697,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CF7F25A-0145-E049-BABB-6C723A859E1D}">
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="27.5" bestFit="1" customWidth="1"/>
@@ -1038,6 +1050,32 @@
         <v>0</v>
       </c>
     </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" t="s">
+        <v>73</v>
+      </c>
+      <c r="C14" t="s">
+        <v>74</v>
+      </c>
+      <c r="D14" t="s">
+        <v>76</v>
+      </c>
+      <c r="E14" t="s">
+        <v>32</v>
+      </c>
+      <c r="F14" t="s">
+        <v>75</v>
+      </c>
+      <c r="G14" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H14" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1045,7 +1083,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{462F859E-7489-7142-8B02-E1AE063A22DB}">
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="22.33203125" bestFit="1" customWidth="1"/>
@@ -1192,6 +1230,17 @@
         <v>53</v>
       </c>
       <c r="C13" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" t="s">
+        <v>74</v>
+      </c>
+      <c r="C14" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1240,7 +1289,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{279D8F2B-ACF8-DF40-AE6A-EC20C786574F}">
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="33.33203125" customWidth="1"/>
@@ -1390,6 +1439,17 @@
         <v>53</v>
       </c>
     </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" t="s">
+        <v>74</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1397,7 +1457,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2E44C3F-3A12-F647-BCB1-FF7A86E9DA05}">
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="33.33203125" customWidth="1"/>
@@ -1586,6 +1646,20 @@
         <v>17</v>
       </c>
     </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" t="s">
+        <v>74</v>
+      </c>
+      <c r="D14" t="s">
+        <v>17</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/database/excels/myhistory/base-seeder.xlsx
+++ b/database/excels/myhistory/base-seeder.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/monoland/Platform/monoland/database/excels/myhistory/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7AB6C9D-141A-1E46-A66E-6CF39B444C4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3F82B19-F255-FF42-B560-8EE84978BDEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" activeTab="5" xr2:uid="{94E1010F-4E68-D749-BBCF-3803F804C4FE}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" activeTab="1" xr2:uid="{94E1010F-4E68-D749-BBCF-3803F804C4FE}"/>
   </bookViews>
   <sheets>
     <sheet name="module" sheetId="2" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="98">
   <si>
     <t>name</t>
   </si>
@@ -98,9 +98,6 @@
     <t>Jabatan</t>
   </si>
   <si>
-    <t>Keluarga</t>
-  </si>
-  <si>
     <t>event_seat</t>
   </si>
   <si>
@@ -113,9 +110,6 @@
     <t>education</t>
   </si>
   <si>
-    <t>family</t>
-  </si>
-  <si>
     <t>pegawai</t>
   </si>
   <si>
@@ -173,9 +167,6 @@
     <t>myhistory-position</t>
   </si>
   <si>
-    <t>myhistory-family</t>
-  </si>
-  <si>
     <t>myhistory-organization</t>
   </si>
   <si>
@@ -224,9 +215,6 @@
     <t>snippet_folder</t>
   </si>
   <si>
-    <t>local_florist</t>
-  </si>
-  <si>
     <t>corporate_fare</t>
   </si>
   <si>
@@ -261,6 +249,81 @@
   </si>
   <si>
     <t>home_work</t>
+  </si>
+  <si>
+    <t>Riwayat Pasangan</t>
+  </si>
+  <si>
+    <t>Riwayat Orangtua</t>
+  </si>
+  <si>
+    <t>Riwayat Anak</t>
+  </si>
+  <si>
+    <t>myhistory-parents</t>
+  </si>
+  <si>
+    <t>myhistory-couple</t>
+  </si>
+  <si>
+    <t>myhistory-child</t>
+  </si>
+  <si>
+    <t>people</t>
+  </si>
+  <si>
+    <t>groups</t>
+  </si>
+  <si>
+    <t>parents</t>
+  </si>
+  <si>
+    <t>couple</t>
+  </si>
+  <si>
+    <t>child</t>
+  </si>
+  <si>
+    <t>elderly</t>
+  </si>
+  <si>
+    <t>title</t>
+  </si>
+  <si>
+    <t>Sasaran Kinerja Pegawai</t>
+  </si>
+  <si>
+    <t>CPNS/PNS</t>
+  </si>
+  <si>
+    <t>Diklat/Kursus</t>
+  </si>
+  <si>
+    <t>Golongan Pangkat</t>
+  </si>
+  <si>
+    <t>Orangtua</t>
+  </si>
+  <si>
+    <t>Pasangan</t>
+  </si>
+  <si>
+    <t>Anak</t>
+  </si>
+  <si>
+    <t>Pendidikan</t>
+  </si>
+  <si>
+    <t>Penghargaan</t>
+  </si>
+  <si>
+    <t>Peninjauan Masa Kerja</t>
+  </si>
+  <si>
+    <t>C L T N</t>
+  </si>
+  <si>
+    <t>Pindah Instansi</t>
   </si>
 </sst>
 </file>
@@ -669,25 +732,25 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" t="s">
         <v>31</v>
       </c>
-      <c r="B2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D2" t="s">
-        <v>33</v>
-      </c>
       <c r="E2" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="F2" t="b">
         <v>1</v>
       </c>
       <c r="G2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -697,19 +760,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CF7F25A-0145-E049-BABB-6C723A859E1D}">
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="27.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.83203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="51.83203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="10.83203125" style="4"/>
-    <col min="9" max="9" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.5" customWidth="1"/>
+    <col min="4" max="4" width="23.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="51.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="10.83203125" style="4"/>
+    <col min="10" max="10" width="16.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -717,362 +781,459 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s">
         <v>18</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3" t="s">
+        <v>51</v>
+      </c>
+      <c r="H3" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I3" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" t="s">
         <v>42</v>
       </c>
-      <c r="D2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="4" t="b">
+      <c r="E4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G4" t="s">
+        <v>52</v>
+      </c>
+      <c r="H4" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I4" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="H2" s="4" t="b">
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" t="s">
+        <v>89</v>
+      </c>
+      <c r="C5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E5" t="s">
+        <v>60</v>
+      </c>
+      <c r="F5" t="s">
+        <v>30</v>
+      </c>
+      <c r="G5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H5" s="4" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D3" t="s">
-        <v>61</v>
-      </c>
-      <c r="E3" t="s">
-        <v>32</v>
-      </c>
-      <c r="F3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G3" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H3" s="4" t="b">
+      <c r="I5" s="4" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C4" t="s">
-        <v>44</v>
-      </c>
-      <c r="D4" t="s">
-        <v>62</v>
-      </c>
-      <c r="E4" t="s">
-        <v>32</v>
-      </c>
-      <c r="F4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G4" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H4" s="4" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>32</v>
-      </c>
-      <c r="B5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C5" t="s">
-        <v>45</v>
-      </c>
-      <c r="D5" t="s">
-        <v>63</v>
-      </c>
-      <c r="E5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G5" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H5" s="4" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B6" t="s">
         <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="D6" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="E6" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="F6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G6" s="4" t="b">
+        <v>30</v>
+      </c>
+      <c r="G6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H6" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="H6" s="4" t="b">
+      <c r="I6" s="4" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="C7" t="s">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="D7" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="E7" t="s">
-        <v>32</v>
+        <v>84</v>
       </c>
       <c r="F7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G7" s="4" t="b">
-        <v>1</v>
+        <v>30</v>
+      </c>
+      <c r="G7" t="s">
+        <v>81</v>
       </c>
       <c r="H7" s="4" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I7" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B8" t="s">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="C8" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="D8" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="E8" t="s">
-        <v>32</v>
+        <v>79</v>
       </c>
       <c r="F8" t="s">
-        <v>56</v>
-      </c>
-      <c r="G8" s="4" t="b">
-        <v>1</v>
+        <v>30</v>
+      </c>
+      <c r="G8" t="s">
+        <v>82</v>
       </c>
       <c r="H8" s="4" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I8" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B9" t="s">
-        <v>36</v>
+        <v>92</v>
       </c>
       <c r="C9" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="D9" t="s">
-        <v>33</v>
+        <v>78</v>
       </c>
       <c r="E9" t="s">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="F9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G9" s="4" t="b">
+        <v>30</v>
+      </c>
+      <c r="G9" t="s">
+        <v>83</v>
+      </c>
+      <c r="H9" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="H9" s="4" t="b">
+      <c r="I9" s="4" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B10" t="s">
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="C10" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="D10" t="s">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="E10" t="s">
-        <v>32</v>
+        <v>61</v>
       </c>
       <c r="F10" t="s">
-        <v>57</v>
-      </c>
-      <c r="G10" s="4" t="b">
-        <v>0</v>
+        <v>30</v>
+      </c>
+      <c r="G10" t="s">
+        <v>53</v>
       </c>
       <c r="H10" s="4" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I10" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B11" t="s">
-        <v>38</v>
+        <v>93</v>
       </c>
       <c r="C11" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="D11" t="s">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="E11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F11" t="s">
-        <v>58</v>
-      </c>
-      <c r="G11" s="4" t="b">
+        <v>30</v>
+      </c>
+      <c r="G11" t="s">
+        <v>25</v>
+      </c>
+      <c r="H11" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="H11" s="4" t="b">
+      <c r="I11" s="4" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B12" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="C12" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="D12" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="E12" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="F12" t="s">
-        <v>59</v>
-      </c>
-      <c r="G12" s="4" t="b">
+        <v>30</v>
+      </c>
+      <c r="G12" t="s">
+        <v>54</v>
+      </c>
+      <c r="H12" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="H12" s="4" t="b">
+      <c r="I12" s="4" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B13" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="C13" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="D13" t="s">
-        <v>69</v>
+        <v>48</v>
       </c>
       <c r="E13" t="s">
-        <v>32</v>
+        <v>63</v>
       </c>
       <c r="F13" t="s">
-        <v>60</v>
-      </c>
-      <c r="G13" s="4" t="b">
-        <v>1</v>
+        <v>30</v>
+      </c>
+      <c r="G13" t="s">
+        <v>55</v>
       </c>
       <c r="H13" s="4" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I13" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B14" t="s">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="C14" t="s">
-        <v>74</v>
+        <v>38</v>
       </c>
       <c r="D14" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="E14" t="s">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="F14" t="s">
-        <v>75</v>
-      </c>
-      <c r="G14" s="4" t="b">
+        <v>30</v>
+      </c>
+      <c r="G14" t="s">
+        <v>56</v>
+      </c>
+      <c r="H14" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="H14" s="4" t="b">
+      <c r="I14" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" t="s">
+        <v>67</v>
+      </c>
+      <c r="C15" t="s">
+        <v>86</v>
+      </c>
+      <c r="D15" t="s">
+        <v>50</v>
+      </c>
+      <c r="E15" t="s">
+        <v>65</v>
+      </c>
+      <c r="F15" t="s">
+        <v>30</v>
+      </c>
+      <c r="G15" t="s">
+        <v>57</v>
+      </c>
+      <c r="H15" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="I15" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" t="s">
+        <v>97</v>
+      </c>
+      <c r="C16" t="s">
+        <v>69</v>
+      </c>
+      <c r="D16" t="s">
+        <v>70</v>
+      </c>
+      <c r="E16" t="s">
+        <v>72</v>
+      </c>
+      <c r="F16" t="s">
+        <v>30</v>
+      </c>
+      <c r="G16" t="s">
+        <v>71</v>
+      </c>
+      <c r="H16" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I16" s="4" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1083,7 +1244,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{462F859E-7489-7142-8B02-E1AE063A22DB}">
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="22.33203125" bestFit="1" customWidth="1"/>
@@ -1103,10 +1264,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>15</v>
@@ -1114,134 +1275,156 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B7" t="s">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="C7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B8" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="C8" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B9" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="C9" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B10" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C10" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B11" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C11" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B12" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C12" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B13" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B14" t="s">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="C14" t="s">
-        <v>30</v>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" t="s">
+        <v>50</v>
+      </c>
+      <c r="C15" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" t="s">
+        <v>70</v>
+      </c>
+      <c r="C16" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1268,7 +1451,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s">
         <v>2</v>
@@ -1276,10 +1459,10 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -1289,7 +1472,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{279D8F2B-ACF8-DF40-AE6A-EC20C786574F}">
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="33.33203125" customWidth="1"/>
@@ -1309,145 +1492,167 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B7" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>47</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B8" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B10" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B12" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C12" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B13" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C13" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B14" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C14" t="s">
-        <v>74</v>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" t="s">
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -1457,7 +1662,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2E44C3F-3A12-F647-BCB1-FF7A86E9DA05}">
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="33.33203125" customWidth="1"/>
@@ -1480,13 +1685,13 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D2" t="s">
         <v>17</v>
@@ -1494,13 +1699,13 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D3" t="s">
         <v>17</v>
@@ -1508,13 +1713,13 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D4" t="s">
         <v>17</v>
@@ -1522,13 +1727,13 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D5" t="s">
         <v>17</v>
@@ -1536,13 +1741,13 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D6" t="s">
         <v>17</v>
@@ -1550,13 +1755,13 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B7" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="D7" t="s">
         <v>17</v>
@@ -1564,13 +1769,13 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B8" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="D8" t="s">
         <v>17</v>
@@ -1578,13 +1783,13 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="D9" t="s">
         <v>17</v>
@@ -1592,13 +1797,13 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B10" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D10" t="s">
         <v>17</v>
@@ -1606,13 +1811,13 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="D11" t="s">
         <v>17</v>
@@ -1620,13 +1825,13 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B12" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C12" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D12" t="s">
         <v>17</v>
@@ -1634,13 +1839,13 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B13" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C13" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D13" t="s">
         <v>17</v>
@@ -1648,15 +1853,43 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B14" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C14" t="s">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="D14" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" t="s">
+        <v>50</v>
+      </c>
+      <c r="D15" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" t="s">
+        <v>70</v>
+      </c>
+      <c r="D16" t="s">
         <v>17</v>
       </c>
     </row>
